--- a/quizzes/019_isolationism_knowledge_quiz--quizzes.xlsx
+++ b/quizzes/019_isolationism_knowledge_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>quiz_answer_1</t>
+          <t>quiz_question_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>What is the main idea behind isolationism?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,23 +561,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>quiz_question_2</t>
+          <t>quiz_question_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What is the main idea behind isolationism?</t>
+          <t>How does isolationism relate to nationalism?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>quiz_answer_2</t>
+          <t>quiz_question_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>What are the main benefits of isolationism?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>quiz_question_3</t>
+          <t>quiz_question_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What are the main benefits of isolationism?</t>
+          <t>What are the main drawbacks of isolationism?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>quiz_answer_3</t>
+          <t>quiz_question_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>How does isolationism affect global economy?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,46 +653,46 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>quiz_question_4</t>
+          <t>quiz_question_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What are the main drawbacks of isolationism?</t>
+          <t>Which of the following is an example of isolationism?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>quiz_answer_4</t>
+          <t>quiz_question_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>What are the different types of isolationism?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>quiz_question_5</t>
+          <t>quiz_question_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>How is isolationism related to nationalism?</t>
+          <t>Why is it important to study isolationism?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>quiz_answer_5</t>
+          <t>quiz_question_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>What are the long-term consequences of isolationism?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>quiz_question_6</t>
+          <t>quiz_question_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What are the different types of isolationism?</t>
+          <t>Isolationism can be seen as a form of protectionism?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>quiz_answer_6</t>
+          <t>quiz_question_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>How does isolationism impact international relations?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,23 +791,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>quiz_question_7</t>
+          <t>quiz_question_13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Which of the following is an example of isolationism?</t>
+          <t>What is the relationship between isolationism and global trade?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>quiz_answer_7</t>
+          <t>quiz_question_14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>What are the benefits of global cooperation over isolationism?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>quiz_question_8</t>
+          <t>quiz_question_15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>What are the main goals of isolationist nations?</t>
+          <t>How can global economy be affected by isolationism?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>quiz_answer_8</t>
+          <t>quiz_question_16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>How does isolationism impact international economic growth?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,230 +883,46 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>quiz_question_9</t>
+          <t>quiz_question_17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Which of the following is not an example of isolationism?</t>
+          <t>What are the main differences between isolationism and globalization?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>quiz_answer_9</t>
+          <t>quiz_question_18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>Isolationism can be seen as a form of?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>quiz_question_10</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>How does isolationism affect global economy?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>quiz_answer_10</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>quiz_question_11</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Isolationism can be seen as a form of</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
           <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>quiz_answer_11</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>quiz_question_12</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>What are the long term consequences of isolationism?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>quiz_answer_12</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>quiz_question_13</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Why is it important to study isolationism?</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>quiz_answer_13</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
         </is>
       </c>
     </row>
@@ -1121,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1149,51 +965,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>quiz_question_6_choices</t>
+          <t>quiz_question_3_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>isolationism_supports_nationalism</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Isolationism supports nationalism</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>quiz_question_6_choices</t>
+          <t>quiz_question_3_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>isolationism_opposes_nationalism</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>Isolationism opposes nationalism</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>quiz_question_6_choices</t>
+          <t>quiz_question_3_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>isolationism_is_unrelated_to_nationalism</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>Isolationism is unrelated to nationalism</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>example_1</t>
+          <t>trade_protection</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>example_1</t>
+          <t>Trade protection</t>
         </is>
       </c>
     </row>
@@ -1222,97 +1038,233 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>example_2</t>
+          <t>tariff_increase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>example_2</t>
+          <t>Tariff increase</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>quiz_question_9_choices</t>
+          <t>quiz_question_7_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>example_1</t>
+          <t>currency_devaluation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>example_1</t>
+          <t>Currency devaluation</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>quiz_question_9_choices</t>
+          <t>quiz_question_7_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>example_2</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>example_2</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>quiz_question_11_choices</t>
+          <t>quiz_question_8_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>economic</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Economic</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>quiz_question_11_choices</t>
+          <t>quiz_question_8_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>political</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>Political</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>quiz_question_8_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>cultural</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Cultural</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>quiz_question_8_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>none_of_the_above</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>None of the above</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>quiz_question_11_choices</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>option_3</t>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>quiz_question_11_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>quiz_question_11_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>maybe</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Maybe</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>quiz_question_18_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>protectionism</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Protectionism</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>quiz_question_18_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>globalization</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Globalization</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>quiz_question_18_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>quiz_question_18_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>none_of_the_above</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
